--- a/data/output/sim_gridrnd/REL1/group_480_40/results/REL1_G2_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_480_40/results/REL1_G2_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,876 +466,997 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S03_G2_482_42_REL1</t>
+          <t>S01_G2_481_40_REL1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D2" t="n">
-        <v>62.26834692364714</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>483.1292777163688</v>
-      </c>
-      <c r="J2" t="n">
-        <v>33.08749482255644</v>
-      </c>
-      <c r="K2" t="n">
-        <v>482.6362700159031</v>
-      </c>
-      <c r="L2" t="n">
-        <v>34.59447878106377</v>
-      </c>
-      <c r="M2" t="n">
-        <v>480.0069291561022</v>
-      </c>
-      <c r="N2" t="n">
-        <v>37.75789265895484</v>
-      </c>
-      <c r="O2" t="n">
-        <v>481.3420568821155</v>
-      </c>
-      <c r="P2" t="n">
-        <v>45.99994413806148</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>477.3260847823025</v>
-      </c>
       <c r="R2" t="n">
-        <v>54.55894519166414</v>
+        <v>489.49</v>
       </c>
       <c r="S2" t="n">
-        <v>478.1928739347501</v>
+        <v>27.84</v>
       </c>
       <c r="T2" t="n">
-        <v>52.27849552327277</v>
+        <v>488.21</v>
       </c>
       <c r="U2" t="n">
-        <v>485.143799404257</v>
+        <v>34.11</v>
       </c>
       <c r="V2" t="n">
-        <v>51.39929702512163</v>
+        <v>483.82</v>
       </c>
       <c r="W2" t="n">
-        <v>485.3417925682962</v>
+        <v>44.78</v>
       </c>
       <c r="X2" t="n">
-        <v>50.16843191203633</v>
+        <v>481.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>482.6162632342611</v>
+        <v>43.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>49.68166645050865</v>
+        <v>485.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>47.18</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>486.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>45.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>480.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>480.52</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>44.51</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>477.16</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>42.87</v>
       </c>
       <c r="AJ2" t="n">
-        <v>498.075</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>499.2833333333334</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>499.025</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>498.82</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>498.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>498.5857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>496.50625</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>495.5</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>496.38</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>51.75634622923067</v>
+        <v>495.85</v>
       </c>
       <c r="AT2" t="n">
-        <v>49.69946064987918</v>
+        <v>496.4333333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>52.52617799726152</v>
+        <v>498.475</v>
       </c>
       <c r="AV2" t="n">
-        <v>57.48536857322914</v>
+        <v>498.39</v>
       </c>
       <c r="AW2" t="n">
-        <v>65.00124785126992</v>
+        <v>499.7416666666667</v>
       </c>
       <c r="AX2" t="n">
-        <v>67.4332459033467</v>
+        <v>499.9571428571429</v>
       </c>
       <c r="AY2" t="n">
-        <v>67.54211620120812</v>
+        <v>500.96875</v>
       </c>
       <c r="AZ2" t="n">
-        <v>66.96578728475211</v>
+        <v>500.5722222222222</v>
       </c>
       <c r="BA2" t="n">
-        <v>65.98678352518783</v>
+        <v>501.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>339</v>
+        <v>56.15405150120515</v>
       </c>
       <c r="BC2" t="n">
-        <v>339</v>
+        <v>54.49965341378074</v>
       </c>
       <c r="BD2" t="n">
-        <v>339</v>
+        <v>54.79255766068965</v>
       </c>
       <c r="BE2" t="n">
-        <v>339</v>
+        <v>59.98081276541691</v>
       </c>
       <c r="BF2" t="n">
-        <v>339</v>
+        <v>58.43108416949169</v>
       </c>
       <c r="BG2" t="n">
-        <v>339</v>
+        <v>60.19561818753581</v>
       </c>
       <c r="BH2" t="n">
-        <v>339</v>
+        <v>59.91748720897348</v>
       </c>
       <c r="BI2" t="n">
-        <v>339</v>
+        <v>58.19068563835391</v>
       </c>
       <c r="BJ2" t="n">
-        <v>339</v>
+        <v>57.09737209364368</v>
       </c>
       <c r="BK2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BL2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BM2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BN2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BO2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BP2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BQ2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BR2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BS2" t="n">
-        <v>636</v>
+        <v>324</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.125</v>
+        <v>612</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.8461538461538461</v>
+        <v>612</v>
       </c>
       <c r="BV2" t="n">
+        <v>612</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>612</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>612</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>612</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>612</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>612</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>612</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CD2" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BW2" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.9411764705882353</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.8421052631578947</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.95</v>
+      <c r="CE2" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>477.16</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>42.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G2_481_40_REL1</t>
+          <t>S02_G2_482_42_REL1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D3" t="n">
-        <v>59.30318754633062</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>489.4850128815723</v>
-      </c>
-      <c r="J3" t="n">
-        <v>27.84229408742188</v>
-      </c>
-      <c r="K3" t="n">
-        <v>488.2090923049701</v>
-      </c>
-      <c r="L3" t="n">
-        <v>34.10904567258947</v>
-      </c>
-      <c r="M3" t="n">
-        <v>483.8215459361376</v>
-      </c>
-      <c r="N3" t="n">
-        <v>44.7774880475806</v>
-      </c>
-      <c r="O3" t="n">
-        <v>481.024315638081</v>
-      </c>
-      <c r="P3" t="n">
-        <v>43.26717936020486</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>485.5653871392619</v>
-      </c>
       <c r="R3" t="n">
-        <v>47.17914406241587</v>
+        <v>470.8</v>
       </c>
       <c r="S3" t="n">
-        <v>486.0903180191513</v>
+        <v>32.22</v>
       </c>
       <c r="T3" t="n">
-        <v>45.89586804785272</v>
+        <v>464.55</v>
       </c>
       <c r="U3" t="n">
-        <v>480.2289081797591</v>
+        <v>47.18</v>
       </c>
       <c r="V3" t="n">
-        <v>46.32846732938514</v>
+        <v>469.4</v>
       </c>
       <c r="W3" t="n">
-        <v>480.5198994482313</v>
+        <v>39.53</v>
       </c>
       <c r="X3" t="n">
-        <v>44.51065183205233</v>
+        <v>475.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>477.1631158940594</v>
+        <v>42.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>42.86902556539994</v>
+        <v>479.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>42.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>479.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>41.81</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>478.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>46.31</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>478.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>47.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>480.48</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>44.76</v>
       </c>
       <c r="AJ3" t="n">
-        <v>495.85</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>496.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>498.475</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>498.39</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>499.7416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>499.9571428571429</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>500.96875</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>500.5722222222222</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>501.01</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>56.15405150120515</v>
+        <v>499.175</v>
       </c>
       <c r="AT3" t="n">
-        <v>54.49965341378074</v>
+        <v>499.1333333333333</v>
       </c>
       <c r="AU3" t="n">
-        <v>54.79255766068965</v>
+        <v>499.6375</v>
       </c>
       <c r="AV3" t="n">
-        <v>59.98081276541691</v>
+        <v>499.24</v>
       </c>
       <c r="AW3" t="n">
-        <v>58.43108416949169</v>
+        <v>499.1166666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>60.19561818753581</v>
+        <v>498.9714285714286</v>
       </c>
       <c r="AY3" t="n">
-        <v>59.91748720897348</v>
+        <v>499.15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>58.19068563835391</v>
+        <v>499.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>57.09737209364368</v>
+        <v>499.29</v>
       </c>
       <c r="BB3" t="n">
-        <v>324</v>
+        <v>61.51174176529226</v>
       </c>
       <c r="BC3" t="n">
-        <v>324</v>
+        <v>58.87853787435811</v>
       </c>
       <c r="BD3" t="n">
-        <v>324</v>
+        <v>56.65426809826423</v>
       </c>
       <c r="BE3" t="n">
-        <v>324</v>
+        <v>55.3344594262924</v>
       </c>
       <c r="BF3" t="n">
-        <v>324</v>
+        <v>53.53630907047</v>
       </c>
       <c r="BG3" t="n">
-        <v>324</v>
+        <v>52.79596072984897</v>
       </c>
       <c r="BH3" t="n">
-        <v>324</v>
+        <v>54.02050536601819</v>
       </c>
       <c r="BI3" t="n">
-        <v>324</v>
+        <v>56.75898362569772</v>
       </c>
       <c r="BJ3" t="n">
-        <v>324</v>
+        <v>57.39796076517005</v>
       </c>
       <c r="BK3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BL3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BM3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BN3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BO3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BP3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BQ3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BR3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BS3" t="n">
-        <v>612</v>
+        <v>341</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.5714285714285714</v>
+        <v>636</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.6875</v>
+        <v>636</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.05555555555555555</v>
+        <v>636</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.7777777777777778</v>
+        <v>636</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.9444444444444444</v>
+        <v>636</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.8181818181818182</v>
+        <v>636</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.6923076923076923</v>
+        <v>636</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.6428571428571429</v>
+        <v>636</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.75</v>
+        <v>636</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.6585365853658537</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.8043478260869565</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>480.48</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>44.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S02_G2_482_42_REL1</t>
+          <t>S03_G2_482_42_REL1</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>482</v>
       </c>
       <c r="C4" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D4" t="n">
         <v>42</v>
-      </c>
-      <c r="D4" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E4" t="n">
         <v>482</v>
@@ -1344,244 +1465,277 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>470.8018073794592</v>
-      </c>
-      <c r="J4" t="n">
-        <v>32.21505555870553</v>
-      </c>
-      <c r="K4" t="n">
-        <v>464.5487431027328</v>
-      </c>
-      <c r="L4" t="n">
-        <v>47.18380943058409</v>
-      </c>
-      <c r="M4" t="n">
-        <v>469.401830691354</v>
-      </c>
-      <c r="N4" t="n">
-        <v>39.5277120552998</v>
-      </c>
-      <c r="O4" t="n">
-        <v>475.0342368957624</v>
-      </c>
-      <c r="P4" t="n">
-        <v>42.4740453421597</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>479.5232778072893</v>
-      </c>
       <c r="R4" t="n">
-        <v>42.02673682776614</v>
+        <v>483.13</v>
       </c>
       <c r="S4" t="n">
-        <v>479.206736488327</v>
+        <v>33.09</v>
       </c>
       <c r="T4" t="n">
-        <v>41.80735466182008</v>
+        <v>482.64</v>
       </c>
       <c r="U4" t="n">
-        <v>478.2434655705367</v>
+        <v>34.59</v>
       </c>
       <c r="V4" t="n">
-        <v>46.3100642517038</v>
+        <v>480.01</v>
       </c>
       <c r="W4" t="n">
-        <v>478.4419774472415</v>
+        <v>37.76</v>
       </c>
       <c r="X4" t="n">
-        <v>47.32254242060588</v>
+        <v>481.34</v>
       </c>
       <c r="Y4" t="n">
-        <v>480.4809037046313</v>
+        <v>46</v>
       </c>
       <c r="Z4" t="n">
-        <v>44.76284328118025</v>
+        <v>477.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>54.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>478.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>52.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>485.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>51.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>485.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>50.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>482.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>49.68</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499.175</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>499.1333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>499.6375</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>499.24</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>499.1166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>498.9714285714286</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>499.15</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>499.2</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>499.29</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>61.51174176529226</v>
+        <v>498.075</v>
       </c>
       <c r="AT4" t="n">
-        <v>58.87853787435811</v>
+        <v>499.2833333333334</v>
       </c>
       <c r="AU4" t="n">
-        <v>56.65426809826423</v>
+        <v>499.025</v>
       </c>
       <c r="AV4" t="n">
-        <v>55.3344594262924</v>
+        <v>498.82</v>
       </c>
       <c r="AW4" t="n">
-        <v>53.53630907047</v>
+        <v>498.4333333333333</v>
       </c>
       <c r="AX4" t="n">
-        <v>52.79596072984897</v>
+        <v>498.5857142857143</v>
       </c>
       <c r="AY4" t="n">
-        <v>54.02050536601819</v>
+        <v>496.50625</v>
       </c>
       <c r="AZ4" t="n">
-        <v>56.75898362569772</v>
+        <v>495.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>57.39796076517005</v>
+        <v>496.38</v>
       </c>
       <c r="BB4" t="n">
-        <v>341</v>
+        <v>51.75634622923067</v>
       </c>
       <c r="BC4" t="n">
-        <v>341</v>
+        <v>49.69946064987918</v>
       </c>
       <c r="BD4" t="n">
-        <v>341</v>
+        <v>52.52617799726152</v>
       </c>
       <c r="BE4" t="n">
-        <v>341</v>
+        <v>57.48536857322914</v>
       </c>
       <c r="BF4" t="n">
-        <v>341</v>
+        <v>65.00124785126992</v>
       </c>
       <c r="BG4" t="n">
-        <v>341</v>
+        <v>67.4332459033467</v>
       </c>
       <c r="BH4" t="n">
-        <v>341</v>
+        <v>67.54211620120812</v>
       </c>
       <c r="BI4" t="n">
-        <v>341</v>
+        <v>66.96578728475211</v>
       </c>
       <c r="BJ4" t="n">
-        <v>341</v>
+        <v>65.98678352518783</v>
       </c>
       <c r="BK4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>339</v>
+      </c>
+      <c r="BT4" t="n">
         <v>636</v>
       </c>
-      <c r="BL4" t="n">
+      <c r="BU4" t="n">
         <v>636</v>
       </c>
-      <c r="BM4" t="n">
+      <c r="BV4" t="n">
         <v>636</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BW4" t="n">
         <v>636</v>
       </c>
-      <c r="BO4" t="n">
+      <c r="BX4" t="n">
         <v>636</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BY4" t="n">
         <v>636</v>
       </c>
-      <c r="BQ4" t="n">
+      <c r="BZ4" t="n">
         <v>636</v>
       </c>
-      <c r="BR4" t="n">
+      <c r="CA4" t="n">
         <v>636</v>
       </c>
-      <c r="BS4" t="n">
+      <c r="CB4" t="n">
         <v>636</v>
       </c>
-      <c r="BT4" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0.7307692307692307</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0.6585365853658537</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.7608695652173914</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.7608695652173914</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>0.8043478260869565</v>
+      <c r="CC4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>482.62</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>49.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G2_480_41_REL1</t>
+          <t>S04_G2_480_39_REL1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>480</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D5" t="n">
-        <v>60.78576723498888</v>
+        <v>39</v>
       </c>
       <c r="E5" t="n">
         <v>480</v>
@@ -1590,244 +1744,277 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>499.1635070218719</v>
-      </c>
-      <c r="J5" t="n">
-        <v>35.56626537763885</v>
-      </c>
-      <c r="K5" t="n">
-        <v>485.7094917662817</v>
-      </c>
-      <c r="L5" t="n">
-        <v>38.82814295296858</v>
-      </c>
-      <c r="M5" t="n">
-        <v>483.8035836506469</v>
-      </c>
-      <c r="N5" t="n">
-        <v>43.7211623770793</v>
-      </c>
-      <c r="O5" t="n">
-        <v>485.5302369413162</v>
-      </c>
-      <c r="P5" t="n">
-        <v>50.37163082589618</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>480.2924010849354</v>
-      </c>
       <c r="R5" t="n">
-        <v>52.8506097595893</v>
+        <v>471.87</v>
       </c>
       <c r="S5" t="n">
-        <v>486.2581153863888</v>
+        <v>37.07</v>
       </c>
       <c r="T5" t="n">
-        <v>49.84764291924116</v>
+        <v>475.66</v>
       </c>
       <c r="U5" t="n">
-        <v>483.9651805147386</v>
+        <v>37.95</v>
       </c>
       <c r="V5" t="n">
-        <v>49.38654128917269</v>
+        <v>479.86</v>
       </c>
       <c r="W5" t="n">
-        <v>483.224830275606</v>
+        <v>37.3</v>
       </c>
       <c r="X5" t="n">
-        <v>48.40903725707975</v>
+        <v>477.93</v>
       </c>
       <c r="Y5" t="n">
-        <v>483.9238785451296</v>
+        <v>34.02</v>
       </c>
       <c r="Z5" t="n">
-        <v>45.9407000966097</v>
+        <v>478.59</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>35.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>474.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>39.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>478.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>40.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>476.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>38.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>476.72</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>40.18</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500.625</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>500.3666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>499.9375</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>500.26</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>500.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>499.6285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>498.96875</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>498.95</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>499.33</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>59.97194656670734</v>
+        <v>492.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>54.45394588294059</v>
+        <v>494.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>52.08318916646714</v>
+        <v>496.5625</v>
       </c>
       <c r="AV5" t="n">
-        <v>59.0871593495575</v>
+        <v>497.93</v>
       </c>
       <c r="AW5" t="n">
-        <v>65.81514305656074</v>
+        <v>498.0666666666667</v>
       </c>
       <c r="AX5" t="n">
-        <v>65.88229144869365</v>
+        <v>498.1928571428571</v>
       </c>
       <c r="AY5" t="n">
-        <v>65.69126862405308</v>
+        <v>497.40625</v>
       </c>
       <c r="AZ5" t="n">
-        <v>64.35148923425679</v>
+        <v>498.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>64.2660960382689</v>
+        <v>498.73</v>
       </c>
       <c r="BB5" t="n">
-        <v>375</v>
+        <v>56.23833212320579</v>
       </c>
       <c r="BC5" t="n">
-        <v>375</v>
+        <v>57.8111004335096</v>
       </c>
       <c r="BD5" t="n">
-        <v>375</v>
+        <v>56.07781284741765</v>
       </c>
       <c r="BE5" t="n">
-        <v>375</v>
+        <v>52.6923628242272</v>
       </c>
       <c r="BF5" t="n">
-        <v>375</v>
+        <v>48.89371693331931</v>
       </c>
       <c r="BG5" t="n">
-        <v>375</v>
+        <v>56.39210892473868</v>
       </c>
       <c r="BH5" t="n">
-        <v>375</v>
+        <v>58.95276677932512</v>
       </c>
       <c r="BI5" t="n">
-        <v>375</v>
+        <v>57.78878207172507</v>
       </c>
       <c r="BJ5" t="n">
-        <v>375</v>
+        <v>57.04180133901804</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>330</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.07142857142857142</v>
+        <v>589</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.5</v>
+        <v>589</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.5</v>
+        <v>589</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.5294117647058824</v>
+        <v>589</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.5294117647058824</v>
+        <v>589</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.5294117647058824</v>
+        <v>592</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.6176470588235294</v>
+        <v>594</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.6176470588235294</v>
+        <v>594</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.6176470588235294</v>
+        <v>594</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>476.72</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>40.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S04_G2_480_39_REL1</t>
+          <t>S05_G2_480_41_REL1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D6" t="n">
-        <v>57.82060785767235</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
         <v>480</v>
@@ -1836,228 +2023,261 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>471.8688710188765</v>
-      </c>
-      <c r="J6" t="n">
-        <v>37.06813261067268</v>
-      </c>
-      <c r="K6" t="n">
-        <v>475.6628928979987</v>
-      </c>
-      <c r="L6" t="n">
-        <v>37.94557753998438</v>
-      </c>
-      <c r="M6" t="n">
-        <v>479.8632866226419</v>
-      </c>
-      <c r="N6" t="n">
-        <v>37.29594876220893</v>
-      </c>
-      <c r="O6" t="n">
-        <v>477.9291272403987</v>
-      </c>
-      <c r="P6" t="n">
-        <v>34.01903650328286</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>478.5875771924569</v>
-      </c>
       <c r="R6" t="n">
-        <v>35.0595400991337</v>
+        <v>499.16</v>
       </c>
       <c r="S6" t="n">
-        <v>474.3802738121221</v>
+        <v>35.57</v>
       </c>
       <c r="T6" t="n">
-        <v>39.06832752246905</v>
+        <v>485.71</v>
       </c>
       <c r="U6" t="n">
-        <v>478.2138956730565</v>
+        <v>38.83</v>
       </c>
       <c r="V6" t="n">
-        <v>40.13511576024144</v>
+        <v>483.8</v>
       </c>
       <c r="W6" t="n">
-        <v>476.4028258569053</v>
+        <v>43.72</v>
       </c>
       <c r="X6" t="n">
-        <v>38.20206628921169</v>
+        <v>485.53</v>
       </c>
       <c r="Y6" t="n">
-        <v>476.7183978045601</v>
+        <v>50.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>40.18386790807261</v>
+        <v>480.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>52.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>486.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>49.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>483.97</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>49.39</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>483.22</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>48.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>483.92</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>45.94</v>
       </c>
       <c r="AJ6" t="n">
-        <v>492.5</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>494.9</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>496.5625</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>497.93</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>498.0666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>498.1928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>497.40625</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>498.3</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>498.73</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>56.23833212320579</v>
+        <v>500.625</v>
       </c>
       <c r="AT6" t="n">
-        <v>57.8111004335096</v>
+        <v>500.3666666666667</v>
       </c>
       <c r="AU6" t="n">
-        <v>56.07781284741765</v>
+        <v>499.9375</v>
       </c>
       <c r="AV6" t="n">
-        <v>52.6923628242272</v>
+        <v>500.26</v>
       </c>
       <c r="AW6" t="n">
-        <v>48.89371693331931</v>
+        <v>500.4833333333333</v>
       </c>
       <c r="AX6" t="n">
-        <v>56.39210892473868</v>
+        <v>499.6285714285714</v>
       </c>
       <c r="AY6" t="n">
-        <v>58.95276677932512</v>
+        <v>498.96875</v>
       </c>
       <c r="AZ6" t="n">
-        <v>57.78878207172507</v>
+        <v>498.95</v>
       </c>
       <c r="BA6" t="n">
-        <v>57.04180133901804</v>
+        <v>499.33</v>
       </c>
       <c r="BB6" t="n">
-        <v>330</v>
+        <v>59.97194656670734</v>
       </c>
       <c r="BC6" t="n">
-        <v>330</v>
+        <v>54.45394588294059</v>
       </c>
       <c r="BD6" t="n">
-        <v>330</v>
+        <v>52.08318916646714</v>
       </c>
       <c r="BE6" t="n">
-        <v>330</v>
+        <v>59.0871593495575</v>
       </c>
       <c r="BF6" t="n">
-        <v>330</v>
+        <v>65.81514305656074</v>
       </c>
       <c r="BG6" t="n">
-        <v>330</v>
+        <v>65.88229144869365</v>
       </c>
       <c r="BH6" t="n">
-        <v>330</v>
+        <v>65.69126862405308</v>
       </c>
       <c r="BI6" t="n">
-        <v>330</v>
+        <v>64.35148923425679</v>
       </c>
       <c r="BJ6" t="n">
-        <v>330</v>
+        <v>64.2660960382689</v>
       </c>
       <c r="BK6" t="n">
-        <v>589</v>
+        <v>375</v>
       </c>
       <c r="BL6" t="n">
-        <v>589</v>
+        <v>375</v>
       </c>
       <c r="BM6" t="n">
-        <v>589</v>
+        <v>375</v>
       </c>
       <c r="BN6" t="n">
-        <v>589</v>
+        <v>375</v>
       </c>
       <c r="BO6" t="n">
-        <v>589</v>
+        <v>375</v>
       </c>
       <c r="BP6" t="n">
-        <v>592</v>
+        <v>375</v>
       </c>
       <c r="BQ6" t="n">
-        <v>594</v>
+        <v>375</v>
       </c>
       <c r="BR6" t="n">
-        <v>594</v>
+        <v>375</v>
       </c>
       <c r="BS6" t="n">
-        <v>594</v>
+        <v>375</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.6428571428571429</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.7857142857142857</v>
+        <v>669</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.9444444444444444</v>
+        <v>669</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.8095238095238095</v>
+        <v>669</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.8095238095238095</v>
+        <v>669</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.9523809523809523</v>
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>483.92</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>45.94</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>482</v>
       </c>
       <c r="C7" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D7" t="n">
         <v>39</v>
-      </c>
-      <c r="D7" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E7" t="n">
         <v>482</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>476.9728321767928</v>
-      </c>
-      <c r="J7" t="n">
-        <v>20.22745368137603</v>
-      </c>
-      <c r="K7" t="n">
-        <v>479.5143790552563</v>
-      </c>
-      <c r="L7" t="n">
-        <v>30.85551536134654</v>
-      </c>
-      <c r="M7" t="n">
-        <v>485.0323831245935</v>
-      </c>
-      <c r="N7" t="n">
-        <v>38.56695772816586</v>
-      </c>
-      <c r="O7" t="n">
-        <v>480.9950543267139</v>
-      </c>
-      <c r="P7" t="n">
-        <v>40.42062436688196</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>485.0160007244215</v>
-      </c>
       <c r="R7" t="n">
-        <v>41.07714580035856</v>
+        <v>476.97</v>
       </c>
       <c r="S7" t="n">
-        <v>487.0697570170601</v>
+        <v>20.23</v>
       </c>
       <c r="T7" t="n">
-        <v>40.05016317973047</v>
+        <v>479.51</v>
       </c>
       <c r="U7" t="n">
-        <v>489.0554594481995</v>
+        <v>30.86</v>
       </c>
       <c r="V7" t="n">
-        <v>37.82835686751925</v>
+        <v>485.03</v>
       </c>
       <c r="W7" t="n">
-        <v>490.8065692637327</v>
+        <v>38.57</v>
       </c>
       <c r="X7" t="n">
-        <v>35.79834295063954</v>
+        <v>481</v>
       </c>
       <c r="Y7" t="n">
-        <v>493.6275865895324</v>
+        <v>40.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.16275934573165</v>
+        <v>485.02</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>41.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>487.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>40.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>489.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>37.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>490.81</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>35.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>493.63</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>37.16</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>504.05</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>502.5833333333333</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>502.15</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>502.63</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>503.4166666666667</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>503.65</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>502.15625</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>502.1055555555556</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>501.785</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>57.99221930569652</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>53.61383268854741</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>57.85220393381742</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>61.50295196167417</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>57.93683102214764</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>55.99743935472152</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>54.89484799084063</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>53.39428779500484</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>52.06043387256776</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>375</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>375</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>375</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>375</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>375</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>375</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>375</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>375</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>375</v>
       </c>
-      <c r="BK7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>669</v>
-      </c>
       <c r="BT7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.9629629629629629</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>493.63</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>37.16</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>482</v>
       </c>
       <c r="C8" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D8" t="n">
         <v>42</v>
-      </c>
-      <c r="D8" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E8" t="n">
         <v>482</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>496.0893844974231</v>
-      </c>
-      <c r="J8" t="n">
-        <v>24.97919272464465</v>
-      </c>
-      <c r="K8" t="n">
-        <v>497.7484224976632</v>
-      </c>
-      <c r="L8" t="n">
-        <v>39.372271008967</v>
-      </c>
-      <c r="M8" t="n">
-        <v>498.3301480761792</v>
-      </c>
-      <c r="N8" t="n">
-        <v>37.88521011393418</v>
-      </c>
-      <c r="O8" t="n">
-        <v>490.8481494569608</v>
-      </c>
-      <c r="P8" t="n">
-        <v>46.34990830900841</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>494.3632737842511</v>
-      </c>
       <c r="R8" t="n">
-        <v>56.56429743344761</v>
+        <v>496.09</v>
       </c>
       <c r="S8" t="n">
-        <v>493.0770208936763</v>
+        <v>24.98</v>
       </c>
       <c r="T8" t="n">
-        <v>51.66209767106518</v>
+        <v>497.75</v>
       </c>
       <c r="U8" t="n">
-        <v>494.9400760192611</v>
+        <v>39.37</v>
       </c>
       <c r="V8" t="n">
-        <v>49.45086148338962</v>
+        <v>498.33</v>
       </c>
       <c r="W8" t="n">
-        <v>493.3931218000068</v>
+        <v>37.89</v>
       </c>
       <c r="X8" t="n">
-        <v>58.11583912026774</v>
+        <v>490.85</v>
       </c>
       <c r="Y8" t="n">
-        <v>493.136455700907</v>
+        <v>46.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>55.96859095731988</v>
+        <v>494.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>56.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>493.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>51.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>494.94</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>49.45</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>493.39</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>58.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>493.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>55.97</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>501.25</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>499.8666666666667</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>499.825</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>500.15</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>499.7583333333333</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>499.2857142857143</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>498.8875</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>498.9833333333333</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>499.215</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>47.2745967724739</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>49.87098911747746</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>47.61768972766318</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>49.85646898848734</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>59.82850433159395</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>64.60089403564072</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>64.22888636548201</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>69.05975472170621</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>68.47224821049767</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>327</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>327</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>327</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>327</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>327</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>327</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>327</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>327</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>327</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>639</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>639</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>639</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>639</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>639</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>639</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>639</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>639</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>639</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0.9</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.8571428571428571</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>493.14</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>55.97</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>482</v>
       </c>
       <c r="C9" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D9" t="n">
         <v>42</v>
-      </c>
-      <c r="D9" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E9" t="n">
         <v>482</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>474.1722717235465</v>
-      </c>
-      <c r="J9" t="n">
-        <v>36.88570371816499</v>
-      </c>
-      <c r="K9" t="n">
-        <v>472.3004676730344</v>
-      </c>
-      <c r="L9" t="n">
-        <v>38.84118595440382</v>
-      </c>
-      <c r="M9" t="n">
-        <v>472.8546803667438</v>
-      </c>
-      <c r="N9" t="n">
-        <v>38.66419605424375</v>
-      </c>
-      <c r="O9" t="n">
-        <v>478.4772681488136</v>
-      </c>
-      <c r="P9" t="n">
-        <v>40.19359916707467</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>482.9068977752187</v>
-      </c>
       <c r="R9" t="n">
-        <v>40.51971562718229</v>
+        <v>474.17</v>
       </c>
       <c r="S9" t="n">
-        <v>482.2934509779056</v>
+        <v>36.89</v>
       </c>
       <c r="T9" t="n">
-        <v>48.07688992129556</v>
+        <v>472.3</v>
       </c>
       <c r="U9" t="n">
-        <v>481.2906073760007</v>
+        <v>38.84</v>
       </c>
       <c r="V9" t="n">
-        <v>52.52067195762929</v>
+        <v>472.85</v>
       </c>
       <c r="W9" t="n">
-        <v>482.2525305237274</v>
+        <v>38.66</v>
       </c>
       <c r="X9" t="n">
-        <v>49.34689671952221</v>
+        <v>478.48</v>
       </c>
       <c r="Y9" t="n">
-        <v>483.5917232765012</v>
+        <v>40.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>50.57330416773565</v>
+        <v>482.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>40.52</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>482.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>48.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>481.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>52.52</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>482.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>49.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>483.59</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>50.57</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>499.1</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>498.4833333333333</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>499.0875</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>499.32</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>498.9833333333333</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>499.3142857142857</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>499.5375</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>500.3055555555555</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>501.225</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>57.24412633624519</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>52.81303237732983</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>49.85358406122874</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>48.12231914610932</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>48.61343835699023</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>52.62374338021706</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>60.45255241716433</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>65.23794884218695</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>65.50171276386595</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>335</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>335</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>335</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>335</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>335</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>335</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>335</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>335</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>335</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>637</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>637</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>637</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>637</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>637</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>637</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>637</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>637</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>637</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.4814814814814815</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.5675675675675675</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.5957446808510638</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.5471698113207547</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.5660377358490566</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.5660377358490566</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.5660377358490566</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.5660377358490566</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>483.59</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>50.57</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>479</v>
       </c>
       <c r="C10" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D10" t="n">
         <v>38</v>
-      </c>
-      <c r="D10" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E10" t="n">
         <v>479</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>480.7322181973869</v>
-      </c>
-      <c r="J10" t="n">
-        <v>27.66210805916981</v>
-      </c>
-      <c r="K10" t="n">
-        <v>481.5883961614635</v>
-      </c>
-      <c r="L10" t="n">
-        <v>30.21749381276779</v>
-      </c>
-      <c r="M10" t="n">
-        <v>480.8139160024022</v>
-      </c>
-      <c r="N10" t="n">
-        <v>28.34721347863091</v>
-      </c>
-      <c r="O10" t="n">
-        <v>478.6284587209271</v>
-      </c>
-      <c r="P10" t="n">
-        <v>30.42677310646067</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>480.8409876103009</v>
-      </c>
       <c r="R10" t="n">
-        <v>29.89553577384896</v>
+        <v>480.73</v>
       </c>
       <c r="S10" t="n">
-        <v>482.2845848245796</v>
+        <v>27.66</v>
       </c>
       <c r="T10" t="n">
-        <v>30.54338796048065</v>
+        <v>481.59</v>
       </c>
       <c r="U10" t="n">
-        <v>477.1533127463559</v>
+        <v>30.22</v>
       </c>
       <c r="V10" t="n">
-        <v>32.47036586486804</v>
+        <v>480.81</v>
       </c>
       <c r="W10" t="n">
-        <v>477.9704528759281</v>
+        <v>28.35</v>
       </c>
       <c r="X10" t="n">
-        <v>32.09034527507391</v>
+        <v>478.63</v>
       </c>
       <c r="Y10" t="n">
-        <v>480.4288157347053</v>
+        <v>30.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>34.70611591504684</v>
+        <v>480.84</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>482.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>30.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>477.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>32.47</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>477.97</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>32.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>480.43</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>34.71</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>501.475</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>499.6333333333333</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>499.5875</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>499.12</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>498.4083333333334</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>499.1285714285714</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>499.9625</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>499.9722222222222</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>500.365</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>62.65220965776067</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>55.15462104141612</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>50.80666633179154</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>54.40960944539115</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>52.51531456526647</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>49.08285165442827</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>49.1871283340469</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>48.75772651654021</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>47.98501615087777</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>362</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>362</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>362</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>362</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>362</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>362</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>362</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>362</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>362</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.8</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.6956521739130435</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.72</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.88</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.8928571428571429</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>480.43</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>34.71</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>478</v>
       </c>
       <c r="C11" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D11" t="n">
         <v>39</v>
-      </c>
-      <c r="D11" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E11" t="n">
         <v>478</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>479.7813548996583</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14.75207491639387</v>
-      </c>
-      <c r="K11" t="n">
-        <v>471.4963591115686</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30.14903625178054</v>
-      </c>
-      <c r="M11" t="n">
-        <v>474.5439457884198</v>
-      </c>
-      <c r="N11" t="n">
-        <v>32.99246779069467</v>
-      </c>
-      <c r="O11" t="n">
-        <v>480.9729342971958</v>
-      </c>
-      <c r="P11" t="n">
-        <v>31.2677001641282</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>478.6155817394023</v>
-      </c>
       <c r="R11" t="n">
-        <v>32.56563736034383</v>
+        <v>479.78</v>
       </c>
       <c r="S11" t="n">
-        <v>473.0007421479227</v>
+        <v>14.75</v>
       </c>
       <c r="T11" t="n">
-        <v>33.60614403844641</v>
+        <v>471.5</v>
       </c>
       <c r="U11" t="n">
-        <v>472.0325633196675</v>
+        <v>30.15</v>
       </c>
       <c r="V11" t="n">
-        <v>33.65779003371334</v>
+        <v>474.54</v>
       </c>
       <c r="W11" t="n">
-        <v>472.4454078088313</v>
+        <v>32.99</v>
       </c>
       <c r="X11" t="n">
-        <v>39.07910979379498</v>
+        <v>480.97</v>
       </c>
       <c r="Y11" t="n">
-        <v>470.2852300619297</v>
+        <v>31.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>42.78434942226174</v>
+        <v>478.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>32.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>33.61</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>472.03</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>33.66</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>472.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>39.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>470.29</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>42.78</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>493.575</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>496.2833333333334</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>497.05</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>497.43</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>498.0166666666667</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>497.7214285714286</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>498.36875</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>498.7611111111111</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>498.925</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>51.2478719070363</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>55.52839864029536</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>54.89806462891018</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>55.51616971657898</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>53.50653906040103</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>52.3972556338515</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>52.06841915631297</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>50.72303486022991</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>52.52189424421019</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>317</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>317</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>317</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>317</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>317</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>317</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>317</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>317</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>317</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>574</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>585</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>585</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>585</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>585</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>585</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>585</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>585</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>585</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.125</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.875</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.65</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.7241379310344828</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>470.29</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>42.78</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>481</v>
       </c>
       <c r="C12" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D12" t="n">
         <v>42</v>
-      </c>
-      <c r="D12" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E12" t="n">
         <v>481</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>470.5329438794997</v>
-      </c>
-      <c r="J12" t="n">
-        <v>33.59820185659498</v>
-      </c>
-      <c r="K12" t="n">
-        <v>484.0208813124487</v>
-      </c>
-      <c r="L12" t="n">
-        <v>36.20871462964558</v>
-      </c>
-      <c r="M12" t="n">
-        <v>485.9243704835902</v>
-      </c>
-      <c r="N12" t="n">
-        <v>43.49817216269358</v>
-      </c>
-      <c r="O12" t="n">
-        <v>489.3128520847618</v>
-      </c>
-      <c r="P12" t="n">
-        <v>55.68172732727694</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>487.4484224051819</v>
-      </c>
       <c r="R12" t="n">
-        <v>61.26961351230911</v>
+        <v>470.53</v>
       </c>
       <c r="S12" t="n">
-        <v>491.3078254009354</v>
+        <v>33.6</v>
       </c>
       <c r="T12" t="n">
-        <v>56.11715795294416</v>
+        <v>484.02</v>
       </c>
       <c r="U12" t="n">
-        <v>491.7392916308173</v>
+        <v>36.21</v>
       </c>
       <c r="V12" t="n">
-        <v>51.77773318911888</v>
+        <v>485.92</v>
       </c>
       <c r="W12" t="n">
-        <v>494.8188266580476</v>
+        <v>43.5</v>
       </c>
       <c r="X12" t="n">
-        <v>51.71230482988957</v>
+        <v>489.31</v>
       </c>
       <c r="Y12" t="n">
-        <v>496.5715887371576</v>
+        <v>55.68</v>
       </c>
       <c r="Z12" t="n">
-        <v>49.91276014633656</v>
+        <v>487.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>61.27</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>491.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>56.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>491.74</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>51.78</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>494.82</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>51.71</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>496.57</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>49.91</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>499.975</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>500.6333333333333</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>500.8375</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>501.43</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>501.2916666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>499.6142857142857</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>499.04375</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>499.3333333333333</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>499.215</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>63.15080660609174</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>55.58266116535104</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>52.24544088961256</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>60.16481613035977</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>70.49579134403857</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>74.34346793424285</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>73.60582066615044</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>70.22630086608103</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>67.69814454621337</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>335</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>335</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>335</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>335</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>335</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>335</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>335</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>335</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>335</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>637</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>637</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>637</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>637</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>637</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>637</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>637</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>637</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>637</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.8636363636363636</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.9090909090909091</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>496.57</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>49.91</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>482</v>
       </c>
       <c r="C13" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D13" t="n">
         <v>41</v>
-      </c>
-      <c r="D13" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E13" t="n">
         <v>482</v>
@@ -3558,244 +3976,277 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>475.1843221686873</v>
-      </c>
-      <c r="J13" t="n">
-        <v>50.23737762263774</v>
-      </c>
-      <c r="K13" t="n">
-        <v>474.7754892243918</v>
-      </c>
-      <c r="L13" t="n">
-        <v>40.80821708735425</v>
-      </c>
-      <c r="M13" t="n">
-        <v>477.7428459341879</v>
-      </c>
-      <c r="N13" t="n">
-        <v>38.91936058016393</v>
-      </c>
-      <c r="O13" t="n">
-        <v>485.4994801633875</v>
-      </c>
-      <c r="P13" t="n">
-        <v>43.5602262925417</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>479.1257523538264</v>
-      </c>
       <c r="R13" t="n">
-        <v>41.85897029256466</v>
+        <v>475.18</v>
       </c>
       <c r="S13" t="n">
-        <v>473.2691830329138</v>
+        <v>50.24</v>
       </c>
       <c r="T13" t="n">
-        <v>42.18943398770305</v>
+        <v>474.78</v>
       </c>
       <c r="U13" t="n">
-        <v>471.3612790685692</v>
+        <v>40.81</v>
       </c>
       <c r="V13" t="n">
-        <v>44.03738295079158</v>
+        <v>477.74</v>
       </c>
       <c r="W13" t="n">
-        <v>474.9879578956842</v>
+        <v>38.92</v>
       </c>
       <c r="X13" t="n">
-        <v>43.60210229140561</v>
+        <v>485.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>471.9354919684849</v>
+        <v>43.56</v>
       </c>
       <c r="Z13" t="n">
-        <v>44.48046257204449</v>
+        <v>479.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>41.86</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>473.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>42.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>471.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>44.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>474.99</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>471.94</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>44.48</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>498.05</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>498.5166666666667</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>499.225</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>498.96</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>499.2166666666666</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>500.1214285714286</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>500.13125</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>500.5055555555555</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>500.435</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>78.10632176719116</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>70.91720328821647</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>64.4631629304675</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>59.95246783911401</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>57.80357303450675</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>57.25600004205958</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>58.4691288068969</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>56.05131549870888</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>55.63079879886681</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>331</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>331</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>331</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>331</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>331</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>331</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>331</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>331</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>331</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>637</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>637</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>637</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>637</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>637</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>637</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>637</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>637</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>637</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.6</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.64</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.6774193548387096</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.8064516129032258</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.8064516129032258</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.8387096774193549</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>471.94</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>44.48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S14_G2_478_39_REL1</t>
+          <t>S13_G2_478_38_REL1</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>478</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D14" t="n">
-        <v>57.82060785767235</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
         <v>478</v>
@@ -3804,244 +4255,277 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>480.7744505610572</v>
-      </c>
-      <c r="J14" t="n">
-        <v>40.82211234319497</v>
-      </c>
-      <c r="K14" t="n">
-        <v>480.8554105134904</v>
-      </c>
-      <c r="L14" t="n">
-        <v>35.36427917167149</v>
-      </c>
-      <c r="M14" t="n">
-        <v>479.491375885302</v>
-      </c>
-      <c r="N14" t="n">
-        <v>35.55005722349787</v>
-      </c>
-      <c r="O14" t="n">
-        <v>478.3517147300148</v>
-      </c>
-      <c r="P14" t="n">
-        <v>46.31355244951381</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>480.3853504865169</v>
-      </c>
       <c r="R14" t="n">
-        <v>41.99793319856176</v>
+        <v>472.35</v>
       </c>
       <c r="S14" t="n">
-        <v>478.0827523584879</v>
+        <v>37.77</v>
       </c>
       <c r="T14" t="n">
-        <v>43.68462456748237</v>
+        <v>482.27</v>
       </c>
       <c r="U14" t="n">
-        <v>480.6545798610226</v>
+        <v>48.41</v>
       </c>
       <c r="V14" t="n">
-        <v>45.96277269383169</v>
+        <v>488.78</v>
       </c>
       <c r="W14" t="n">
-        <v>486.0534946810076</v>
+        <v>56.92</v>
       </c>
       <c r="X14" t="n">
-        <v>45.08061650617985</v>
+        <v>486.37</v>
       </c>
       <c r="Y14" t="n">
-        <v>485.5023553110656</v>
+        <v>62.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>44.71823575422533</v>
+        <v>488.07</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>58.26</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>491.84</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>59.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>487.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>55.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>488.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>54.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>485.07</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>57.18</v>
       </c>
       <c r="AJ14" t="n">
-        <v>498.7</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>499.1</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>504.55</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>504.25</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>502.8625</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>501.95</v>
+      </c>
+      <c r="AW14" t="n">
         <v>500.625</v>
       </c>
-      <c r="AM14" t="n">
-        <v>500.31</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>500.1916666666667</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>499.6642857142857</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>500.05625</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>500.1222222222222</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>500.065</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>55.51450260967849</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>53.38248776518381</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>52.08343666656416</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>58.12343675317213</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>58.42349639105447</v>
-      </c>
       <c r="AX14" t="n">
-        <v>56.78551257825811</v>
+        <v>502.1</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.05055289773711</v>
+        <v>502.81875</v>
       </c>
       <c r="AZ14" t="n">
-        <v>55.31231082132676</v>
+        <v>502.5277777777778</v>
       </c>
       <c r="BA14" t="n">
-        <v>54.25680395120966</v>
+        <v>502.255</v>
       </c>
       <c r="BB14" t="n">
-        <v>339</v>
+        <v>72.33876899699082</v>
       </c>
       <c r="BC14" t="n">
-        <v>339</v>
+        <v>63.32183009568396</v>
       </c>
       <c r="BD14" t="n">
-        <v>339</v>
+        <v>65.91542758527778</v>
       </c>
       <c r="BE14" t="n">
-        <v>339</v>
+        <v>76.94561391008587</v>
       </c>
       <c r="BF14" t="n">
-        <v>339</v>
+        <v>74.55312004425659</v>
       </c>
       <c r="BG14" t="n">
-        <v>339</v>
+        <v>71.48439390124653</v>
       </c>
       <c r="BH14" t="n">
-        <v>339</v>
+        <v>71.18961229306913</v>
       </c>
       <c r="BI14" t="n">
-        <v>339</v>
+        <v>68.37701291414922</v>
       </c>
       <c r="BJ14" t="n">
-        <v>339</v>
+        <v>68.53276570371285</v>
       </c>
       <c r="BK14" t="n">
-        <v>636</v>
+        <v>407</v>
       </c>
       <c r="BL14" t="n">
-        <v>636</v>
+        <v>407</v>
       </c>
       <c r="BM14" t="n">
-        <v>636</v>
+        <v>398</v>
       </c>
       <c r="BN14" t="n">
-        <v>636</v>
+        <v>375</v>
       </c>
       <c r="BO14" t="n">
-        <v>636</v>
+        <v>375</v>
       </c>
       <c r="BP14" t="n">
-        <v>636</v>
+        <v>375</v>
       </c>
       <c r="BQ14" t="n">
-        <v>636</v>
+        <v>375</v>
       </c>
       <c r="BR14" t="n">
-        <v>636</v>
+        <v>375</v>
       </c>
       <c r="BS14" t="n">
-        <v>636</v>
+        <v>375</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.9090909090909091</v>
+        <v>669</v>
       </c>
       <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
         <v>1</v>
       </c>
-      <c r="BW14" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>0.8947368421052632</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>0.8709677419354839</v>
+      <c r="CD14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>485.07</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>57.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S13_G2_478_38_REL1</t>
+          <t>S14_G2_478_39_REL1</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>478</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D15" t="n">
-        <v>56.33802816901409</v>
+        <v>39</v>
       </c>
       <c r="E15" t="n">
         <v>478</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>472.3536727097419</v>
-      </c>
-      <c r="J15" t="n">
-        <v>37.77251078143722</v>
-      </c>
-      <c r="K15" t="n">
-        <v>482.273343269019</v>
-      </c>
-      <c r="L15" t="n">
-        <v>48.40523551504351</v>
-      </c>
-      <c r="M15" t="n">
-        <v>488.7801213239172</v>
-      </c>
-      <c r="N15" t="n">
-        <v>56.91560673592314</v>
-      </c>
-      <c r="O15" t="n">
-        <v>486.3670552182688</v>
-      </c>
-      <c r="P15" t="n">
-        <v>62.49204163682117</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>488.0652220588291</v>
-      </c>
       <c r="R15" t="n">
-        <v>58.26356448979087</v>
+        <v>480.77</v>
       </c>
       <c r="S15" t="n">
-        <v>491.8427688369808</v>
+        <v>40.82</v>
       </c>
       <c r="T15" t="n">
-        <v>59.75214372265337</v>
+        <v>480.86</v>
       </c>
       <c r="U15" t="n">
-        <v>487.3423890551289</v>
+        <v>35.36</v>
       </c>
       <c r="V15" t="n">
-        <v>55.951311303537</v>
+        <v>479.49</v>
       </c>
       <c r="W15" t="n">
-        <v>488.197822887709</v>
+        <v>35.55</v>
       </c>
       <c r="X15" t="n">
-        <v>54.1177050610718</v>
+        <v>478.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>485.0664841113219</v>
+        <v>46.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>57.18019649190632</v>
+        <v>480.39</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>478.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>43.68</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>480.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>45.96</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>486.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>45.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>485.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>44.72</v>
       </c>
       <c r="AJ15" t="n">
-        <v>504.55</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>504.25</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>502.8625</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>501.95</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>498.7</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>499.1</v>
+      </c>
+      <c r="AU15" t="n">
         <v>500.625</v>
       </c>
-      <c r="AO15" t="n">
-        <v>502.1</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>502.81875</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>502.5277777777778</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>502.255</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>72.33876899699082</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>63.32183009568396</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>65.91542758527778</v>
-      </c>
       <c r="AV15" t="n">
-        <v>76.94561391008587</v>
+        <v>500.31</v>
       </c>
       <c r="AW15" t="n">
-        <v>74.55312004425659</v>
+        <v>500.1916666666667</v>
       </c>
       <c r="AX15" t="n">
-        <v>71.48439390124653</v>
+        <v>499.6642857142857</v>
       </c>
       <c r="AY15" t="n">
-        <v>71.18961229306913</v>
+        <v>500.05625</v>
       </c>
       <c r="AZ15" t="n">
-        <v>68.37701291414922</v>
+        <v>500.1222222222222</v>
       </c>
       <c r="BA15" t="n">
-        <v>68.53276570371285</v>
+        <v>500.065</v>
       </c>
       <c r="BB15" t="n">
-        <v>407</v>
+        <v>55.51450260967849</v>
       </c>
       <c r="BC15" t="n">
-        <v>407</v>
+        <v>53.38248776518381</v>
       </c>
       <c r="BD15" t="n">
-        <v>398</v>
+        <v>52.08343666656416</v>
       </c>
       <c r="BE15" t="n">
-        <v>375</v>
+        <v>58.12343675317213</v>
       </c>
       <c r="BF15" t="n">
-        <v>375</v>
+        <v>58.42349639105447</v>
       </c>
       <c r="BG15" t="n">
-        <v>375</v>
+        <v>56.78551257825811</v>
       </c>
       <c r="BH15" t="n">
-        <v>375</v>
+        <v>57.05055289773711</v>
       </c>
       <c r="BI15" t="n">
-        <v>375</v>
+        <v>55.31231082132676</v>
       </c>
       <c r="BJ15" t="n">
-        <v>375</v>
+        <v>54.25680395120966</v>
       </c>
       <c r="BK15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BL15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BM15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BN15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BO15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BP15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BQ15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BR15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BS15" t="n">
-        <v>669</v>
+        <v>339</v>
       </c>
       <c r="BT15" t="n">
+        <v>636</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>636</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>636</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>636</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>636</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>636</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>636</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>636</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>636</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CE15" t="n">
         <v>1</v>
       </c>
-      <c r="BU15" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.8421052631578947</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0.8333333333333334</v>
+      <c r="CF15" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>485.5</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>44.72</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>480</v>
       </c>
       <c r="C16" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D16" t="n">
         <v>38</v>
-      </c>
-      <c r="D16" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E16" t="n">
         <v>480</v>
@@ -4296,720 +4813,819 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>500.9196217348791</v>
-      </c>
-      <c r="J16" t="n">
-        <v>30.73066774484752</v>
-      </c>
-      <c r="K16" t="n">
-        <v>495.1323636705923</v>
-      </c>
-      <c r="L16" t="n">
-        <v>24.05744146702282</v>
-      </c>
-      <c r="M16" t="n">
-        <v>490.2407671181049</v>
-      </c>
-      <c r="N16" t="n">
-        <v>28.85733299906883</v>
-      </c>
-      <c r="O16" t="n">
-        <v>487.1575618259299</v>
-      </c>
-      <c r="P16" t="n">
-        <v>29.19874246901368</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>487.7391710518913</v>
-      </c>
       <c r="R16" t="n">
-        <v>29.54070698504194</v>
+        <v>500.92</v>
       </c>
       <c r="S16" t="n">
-        <v>483.1644788571465</v>
+        <v>30.73</v>
       </c>
       <c r="T16" t="n">
-        <v>34.40679423739062</v>
+        <v>495.13</v>
       </c>
       <c r="U16" t="n">
-        <v>480.5652057627818</v>
+        <v>24.06</v>
       </c>
       <c r="V16" t="n">
-        <v>41.14560141029459</v>
+        <v>490.24</v>
       </c>
       <c r="W16" t="n">
-        <v>480.4492648118891</v>
+        <v>28.86</v>
       </c>
       <c r="X16" t="n">
-        <v>39.99804234698787</v>
+        <v>487.16</v>
       </c>
       <c r="Y16" t="n">
-        <v>481.48359116604</v>
+        <v>29.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>39.92155114332803</v>
+        <v>487.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>29.54</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>483.16</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>34.41</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>480.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>41.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>480.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>481.48</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>39.92</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>503.8</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>502.3166666666667</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>501.0375</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>500.67</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>500.9916666666667</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>500.7285714285715</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>500.5875</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>500.7555555555555</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>501.47</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>55.40180502474626</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>48.25573943987274</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>44.3580442958208</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>43.8472473480377</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>45.22692705187426</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>45.15953353819938</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>51.41186481494326</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>56.73942605574894</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>58.91832567206913</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>394</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>394</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>394</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>394</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>394</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>394</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>392</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>392</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>392</v>
       </c>
-      <c r="BK16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>669</v>
-      </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.88</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.96</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.96</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.96</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>481.48</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>39.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S17_G2_481_40_REL1</t>
+          <t>S16_G2_479_38_REL1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D17" t="n">
-        <v>59.30318754633062</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>482.3870303473709</v>
-      </c>
-      <c r="J17" t="n">
-        <v>51.05142476223799</v>
-      </c>
-      <c r="K17" t="n">
-        <v>482.2367494039449</v>
-      </c>
-      <c r="L17" t="n">
-        <v>57.21834669603968</v>
-      </c>
-      <c r="M17" t="n">
-        <v>476.6184877034019</v>
-      </c>
-      <c r="N17" t="n">
-        <v>50.39201833395585</v>
-      </c>
-      <c r="O17" t="n">
-        <v>474.1480999919651</v>
-      </c>
-      <c r="P17" t="n">
-        <v>45.22001959903229</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>470.3256808381773</v>
-      </c>
       <c r="R17" t="n">
-        <v>47.56141720102919</v>
+        <v>491.78</v>
       </c>
       <c r="S17" t="n">
-        <v>474.224498872672</v>
+        <v>44.73</v>
       </c>
       <c r="T17" t="n">
-        <v>49.14150057234598</v>
+        <v>478.34</v>
       </c>
       <c r="U17" t="n">
-        <v>474.687061626824</v>
+        <v>43.04</v>
       </c>
       <c r="V17" t="n">
-        <v>47.28140219900218</v>
+        <v>490.97</v>
       </c>
       <c r="W17" t="n">
-        <v>475.9781272273169</v>
+        <v>41.89</v>
       </c>
       <c r="X17" t="n">
-        <v>46.99050329675117</v>
+        <v>484.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>474.5186348409478</v>
+        <v>46.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>48.22709901103267</v>
+        <v>484.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>43.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>486.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>41.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>488.02</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>39.22</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>490.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>37.56</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>487.86</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>41.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>503.5</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>501.05</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>501.1</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>501.44</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>500.275</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>499.7285714285715</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>499.30625</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>498.9</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>498.865</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>63.96287986011887</v>
+        <v>499.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>62.88545804344064</v>
+        <v>500.2833333333334</v>
       </c>
       <c r="AU17" t="n">
-        <v>66.09644468502069</v>
+        <v>500.425</v>
       </c>
       <c r="AV17" t="n">
-        <v>61.76298567912662</v>
+        <v>501.09</v>
       </c>
       <c r="AW17" t="n">
-        <v>63.7335550684776</v>
+        <v>502.1583333333334</v>
       </c>
       <c r="AX17" t="n">
-        <v>62.73548128646897</v>
+        <v>501.15</v>
       </c>
       <c r="AY17" t="n">
-        <v>61.10257736738689</v>
+        <v>500.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>60.31004154459779</v>
+        <v>499.6055555555556</v>
       </c>
       <c r="BA17" t="n">
-        <v>59.99397282227606</v>
+        <v>500.595</v>
       </c>
       <c r="BB17" t="n">
-        <v>400</v>
+        <v>74.98406497383294</v>
       </c>
       <c r="BC17" t="n">
-        <v>400</v>
+        <v>70.15793888712017</v>
       </c>
       <c r="BD17" t="n">
-        <v>400</v>
+        <v>64.64591537753952</v>
       </c>
       <c r="BE17" t="n">
-        <v>400</v>
+        <v>62.98366375497697</v>
       </c>
       <c r="BF17" t="n">
-        <v>400</v>
+        <v>61.66279210800915</v>
       </c>
       <c r="BG17" t="n">
-        <v>400</v>
+        <v>59.14605710804882</v>
       </c>
       <c r="BH17" t="n">
-        <v>400</v>
+        <v>57.18498491737144</v>
       </c>
       <c r="BI17" t="n">
-        <v>400</v>
+        <v>55.56442679171052</v>
       </c>
       <c r="BJ17" t="n">
-        <v>400</v>
+        <v>55.04426377925315</v>
       </c>
       <c r="BK17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BL17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BM17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BN17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BO17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BP17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BQ17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BR17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BS17" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.7</v>
+        <v>669</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.7857142857142857</v>
+        <v>669</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.9285714285714286</v>
+        <v>669</v>
       </c>
       <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
         <v>1</v>
       </c>
-      <c r="BX17" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0.8421052631578947</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="CA17" t="n">
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CF17" t="n">
         <v>0.875</v>
       </c>
-      <c r="CB17" t="n">
-        <v>0.8846153846153846</v>
+      <c r="CG17" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>487.86</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>41.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S16_G2_479_38_REL1</t>
+          <t>S17_G2_481_40_REL1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D18" t="n">
-        <v>56.33802816901409</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>491.7753243591824</v>
-      </c>
-      <c r="J18" t="n">
-        <v>44.73140620515836</v>
-      </c>
-      <c r="K18" t="n">
-        <v>478.3438393717116</v>
-      </c>
-      <c r="L18" t="n">
-        <v>43.04025003114663</v>
-      </c>
-      <c r="M18" t="n">
-        <v>490.9652386345849</v>
-      </c>
-      <c r="N18" t="n">
-        <v>41.89147002489173</v>
-      </c>
-      <c r="O18" t="n">
-        <v>484.074316734482</v>
-      </c>
-      <c r="P18" t="n">
-        <v>46.32960198653342</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>484.5644933664121</v>
-      </c>
       <c r="R18" t="n">
-        <v>43.98220059957739</v>
+        <v>482.39</v>
       </c>
       <c r="S18" t="n">
-        <v>486.6318286066481</v>
+        <v>51.05</v>
       </c>
       <c r="T18" t="n">
-        <v>41.5494679435961</v>
+        <v>482.24</v>
       </c>
       <c r="U18" t="n">
-        <v>488.0198098910883</v>
+        <v>57.22</v>
       </c>
       <c r="V18" t="n">
-        <v>39.21581535360768</v>
+        <v>476.62</v>
       </c>
       <c r="W18" t="n">
-        <v>490.1038651859838</v>
+        <v>50.39</v>
       </c>
       <c r="X18" t="n">
-        <v>37.55850733670152</v>
+        <v>474.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>487.8561227323767</v>
+        <v>45.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>41.40276129314385</v>
+        <v>470.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>47.56</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>474.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>49.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>474.69</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>47.28</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>475.98</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>46.99</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>474.52</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>48.23</v>
       </c>
       <c r="AJ18" t="n">
-        <v>499.8</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>500.2833333333334</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>500.425</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>501.09</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>502.1583333333334</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>501.15</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>500.2</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>499.6055555555556</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>500.595</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>74.98406497383294</v>
+        <v>503.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>70.15793888712017</v>
+        <v>501.05</v>
       </c>
       <c r="AU18" t="n">
-        <v>64.64591537753952</v>
+        <v>501.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>62.98366375497697</v>
+        <v>501.44</v>
       </c>
       <c r="AW18" t="n">
-        <v>61.66279210800915</v>
+        <v>500.275</v>
       </c>
       <c r="AX18" t="n">
-        <v>59.14605710804882</v>
+        <v>499.7285714285715</v>
       </c>
       <c r="AY18" t="n">
-        <v>57.18498491737144</v>
+        <v>499.30625</v>
       </c>
       <c r="AZ18" t="n">
-        <v>55.56442679171052</v>
+        <v>498.9</v>
       </c>
       <c r="BA18" t="n">
-        <v>55.04426377925315</v>
+        <v>498.865</v>
       </c>
       <c r="BB18" t="n">
-        <v>344</v>
+        <v>63.96287986011887</v>
       </c>
       <c r="BC18" t="n">
-        <v>344</v>
+        <v>62.88545804344064</v>
       </c>
       <c r="BD18" t="n">
-        <v>344</v>
+        <v>66.09644468502069</v>
       </c>
       <c r="BE18" t="n">
-        <v>344</v>
+        <v>61.76298567912662</v>
       </c>
       <c r="BF18" t="n">
-        <v>344</v>
+        <v>63.7335550684776</v>
       </c>
       <c r="BG18" t="n">
-        <v>344</v>
+        <v>62.73548128646897</v>
       </c>
       <c r="BH18" t="n">
-        <v>344</v>
+        <v>61.10257736738689</v>
       </c>
       <c r="BI18" t="n">
-        <v>344</v>
+        <v>60.31004154459779</v>
       </c>
       <c r="BJ18" t="n">
-        <v>344</v>
+        <v>59.99397282227606</v>
       </c>
       <c r="BK18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BL18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BM18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BN18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BO18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BP18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BQ18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BR18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BS18" t="n">
-        <v>669</v>
+        <v>400</v>
       </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CF18" t="n">
         <v>1</v>
       </c>
-      <c r="BU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="BW18" t="n">
+      <c r="CG18" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CJ18" t="n">
         <v>0.875</v>
       </c>
-      <c r="BX18" t="n">
-        <v>0.8947368421052632</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0.8636363636363636</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0.9130434782608695</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>0.9310344827586207</v>
+      <c r="CK18" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>474.52</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>48.23</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>480</v>
       </c>
       <c r="C19" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D19" t="n">
         <v>40</v>
-      </c>
-      <c r="D19" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E19" t="n">
         <v>480</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>474.3667702517835</v>
-      </c>
-      <c r="J19" t="n">
-        <v>32.48963611296246</v>
-      </c>
-      <c r="K19" t="n">
-        <v>471.8710309076839</v>
-      </c>
-      <c r="L19" t="n">
-        <v>55.22329563616168</v>
-      </c>
-      <c r="M19" t="n">
-        <v>473.9617501055558</v>
-      </c>
-      <c r="N19" t="n">
-        <v>47.62427943068594</v>
-      </c>
-      <c r="O19" t="n">
-        <v>474.4485655731191</v>
-      </c>
-      <c r="P19" t="n">
-        <v>45.9398636638818</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>473.6057745895894</v>
-      </c>
       <c r="R19" t="n">
-        <v>47.51358907329907</v>
+        <v>474.37</v>
       </c>
       <c r="S19" t="n">
-        <v>476.0895685554596</v>
+        <v>32.49</v>
       </c>
       <c r="T19" t="n">
-        <v>49.52848177875479</v>
+        <v>471.87</v>
       </c>
       <c r="U19" t="n">
-        <v>476.0060327441724</v>
+        <v>55.22</v>
       </c>
       <c r="V19" t="n">
-        <v>53.01173190483302</v>
+        <v>473.96</v>
       </c>
       <c r="W19" t="n">
-        <v>473.8555827348486</v>
+        <v>47.62</v>
       </c>
       <c r="X19" t="n">
-        <v>51.73524371171256</v>
+        <v>474.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>475.7072846116105</v>
+        <v>45.94</v>
       </c>
       <c r="Z19" t="n">
-        <v>49.62641392577478</v>
+        <v>473.61</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>47.51</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>476.09</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>49.53</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>476.01</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>53.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>473.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>51.74</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>475.71</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>49.63</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>497.65</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>497.2</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>496.8</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>497.12</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>498.2166666666666</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>497.8857142857143</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>497.58125</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>498.7166666666666</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>499.3</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>57.65264521251389</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>59.50848678970085</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>65.95327891773084</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>64.68095237394081</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>62.4664154210529</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>62.90810596352721</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>64.12238999318022</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>64.07836131557117</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>62.1214938648452</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>337</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>337</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>337</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>337</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>337</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>337</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>337</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>337</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>337</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BT19" t="n">
         <v>612</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BU19" t="n">
         <v>612</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BV19" t="n">
         <v>612</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BW19" t="n">
         <v>612</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BX19" t="n">
         <v>612</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BY19" t="n">
         <v>612</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BZ19" t="n">
         <v>612</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="CA19" t="n">
         <v>612</v>
       </c>
-      <c r="BS19" t="n">
+      <c r="CB19" t="n">
         <v>612</v>
       </c>
-      <c r="BT19" t="n">
+      <c r="CC19" t="n">
         <v>1</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>1</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.75</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>1</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.9</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.9230769230769231</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>475.71</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>49.63</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>482</v>
       </c>
       <c r="C20" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D20" t="n">
         <v>39</v>
-      </c>
-      <c r="D20" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E20" t="n">
         <v>482</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>457.2491080770833</v>
-      </c>
-      <c r="J20" t="n">
-        <v>59.13376858546759</v>
-      </c>
-      <c r="K20" t="n">
-        <v>454.0560596853288</v>
-      </c>
-      <c r="L20" t="n">
-        <v>53.04555007850952</v>
-      </c>
-      <c r="M20" t="n">
-        <v>462.1581746357534</v>
-      </c>
-      <c r="N20" t="n">
-        <v>52.05040771104623</v>
-      </c>
-      <c r="O20" t="n">
-        <v>465.0019240684967</v>
-      </c>
-      <c r="P20" t="n">
-        <v>54.05124735886226</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>466.6086292755846</v>
-      </c>
       <c r="R20" t="n">
-        <v>51.07738736507059</v>
+        <v>457.25</v>
       </c>
       <c r="S20" t="n">
-        <v>466.2378278810224</v>
+        <v>59.13</v>
       </c>
       <c r="T20" t="n">
-        <v>48.74579262628016</v>
+        <v>454.06</v>
       </c>
       <c r="U20" t="n">
-        <v>469.0311941439567</v>
+        <v>53.05</v>
       </c>
       <c r="V20" t="n">
-        <v>47.13795820623729</v>
+        <v>462.16</v>
       </c>
       <c r="W20" t="n">
-        <v>472.7199965643607</v>
+        <v>52.05</v>
       </c>
       <c r="X20" t="n">
-        <v>48.18768039451999</v>
+        <v>465</v>
       </c>
       <c r="Y20" t="n">
-        <v>473.3105317712782</v>
+        <v>54.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>46.84382827867486</v>
+        <v>466.61</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>51.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>466.24</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>48.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>469.03</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>47.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>472.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>48.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>473.31</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>46.84</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>501.425</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>501.2666666666667</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>502.3</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>501.47</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>500.4833333333333</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>501.4214285714286</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>501.875</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>501.8555555555556</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>501.48</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>71.86128564811514</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>77.14248001083594</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>72.44884402114364</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>69.62118283970763</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>68.76311794042566</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>66.95788312248901</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>65.2674066820492</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>64.67758689773129</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>61.55696223823914</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>364</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>364</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>364</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>364</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>364</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>364</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>364</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>364</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>364</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>1</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.8</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.9</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.92</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.96</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>473.31</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>46.84</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>480</v>
       </c>
       <c r="C21" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D21" t="n">
         <v>41</v>
-      </c>
-      <c r="D21" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E21" t="n">
         <v>480</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>471.9308532664819</v>
-      </c>
-      <c r="J21" t="n">
-        <v>48.07238156573214</v>
-      </c>
-      <c r="K21" t="n">
-        <v>469.8200226375512</v>
-      </c>
-      <c r="L21" t="n">
-        <v>45.97366957855885</v>
-      </c>
-      <c r="M21" t="n">
-        <v>468.8695814840713</v>
-      </c>
-      <c r="N21" t="n">
-        <v>44.02358054353559</v>
-      </c>
-      <c r="O21" t="n">
-        <v>461.9147413161672</v>
-      </c>
-      <c r="P21" t="n">
-        <v>41.97825835949315</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>463.697516444505</v>
-      </c>
       <c r="R21" t="n">
-        <v>45.95495722183594</v>
+        <v>471.93</v>
       </c>
       <c r="S21" t="n">
-        <v>466.1739336331099</v>
+        <v>48.07</v>
       </c>
       <c r="T21" t="n">
-        <v>44.87516337734394</v>
+        <v>469.82</v>
       </c>
       <c r="U21" t="n">
-        <v>468.5576629651817</v>
+        <v>45.97</v>
       </c>
       <c r="V21" t="n">
-        <v>43.90095447897656</v>
+        <v>468.87</v>
       </c>
       <c r="W21" t="n">
-        <v>467.2863215587556</v>
+        <v>44.02</v>
       </c>
       <c r="X21" t="n">
-        <v>44.44271893897174</v>
+        <v>461.91</v>
       </c>
       <c r="Y21" t="n">
-        <v>467.9485176327326</v>
+        <v>41.98</v>
       </c>
       <c r="Z21" t="n">
-        <v>48.03088452327601</v>
+        <v>463.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>45.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>466.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>44.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>468.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>43.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>467.29</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>44.44</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>467.95</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>48.03</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>503.35</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>502.0166666666667</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>500.9125</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>502.01</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>502.2416666666667</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>501.9714285714286</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>502.6375</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>502.7</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>503.135</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>89.21282138795971</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>77.55718141403084</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>70.99369580286688</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>68.4170293128838</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>69.18345127670024</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>65.49906682619257</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>63.19666600185487</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>62.90432770838939</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>65.95602152192019</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>354</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>354</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>354</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>354</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>354</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>354</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>354</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>354</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>354</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>1</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>1</v>
       </c>
-      <c r="BV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW21" t="n">
+      <c r="CE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF21" t="n">
         <v>1</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>1</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>1</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.8636363636363636</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>1</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>467.95</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>48.03</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>480.45</v>
       </c>
       <c r="C22" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D22" t="n">
         <v>40</v>
-      </c>
-      <c r="D22" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E22" t="n">
         <v>480.45</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>78.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.5985</v>
+      </c>
       <c r="I22" t="n">
-        <v>479.9835317434362</v>
+        <v>2.6905</v>
       </c>
       <c r="J22" t="n">
-        <v>35.94626315685078</v>
+        <v>2.7435</v>
       </c>
       <c r="K22" t="n">
-        <v>478.6399852291517</v>
+        <v>2.783</v>
       </c>
       <c r="L22" t="n">
-        <v>40.0720778328805</v>
+        <v>2.806</v>
       </c>
       <c r="M22" t="n">
-        <v>480.1612481361846</v>
+        <v>2.815</v>
       </c>
       <c r="N22" t="n">
-        <v>40.96292674061278</v>
+        <v>2.459</v>
       </c>
       <c r="O22" t="n">
-        <v>479.8529075127438</v>
+        <v>2.461</v>
       </c>
       <c r="P22" t="n">
-        <v>43.77778612130646</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>480.2301741255176</v>
-      </c>
+        <v>2.4785</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>45.06588239374155</v>
+        <v>479.9830000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>480.443926976863</v>
+        <v>35.9465</v>
       </c>
       <c r="T22" t="n">
-        <v>45.14134661060844</v>
+        <v>478.6405</v>
       </c>
       <c r="U22" t="n">
-        <v>480.4115887500687</v>
+        <v>40.07250000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>45.44550977764874</v>
+        <v>480.16</v>
       </c>
       <c r="W22" t="n">
-        <v>481.2625334037055</v>
+        <v>40.9635</v>
       </c>
       <c r="X22" t="n">
-        <v>45.3234344142238</v>
+        <v>479.8525000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>481.0936486714616</v>
+        <v>43.7775</v>
       </c>
       <c r="Z22" t="n">
-        <v>45.74887081248049</v>
+        <v>480.2320000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>45.066</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>480.4429999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>45.1425</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>480.4115</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>45.4465</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>481.2625000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>45.324</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>481.0945</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>45.748</v>
       </c>
       <c r="AJ22" t="n">
-        <v>499.8237499999999</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>499.68</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>499.8731249999999</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>499.824</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>499.6795</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>499.8734999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>499.987</v>
       </c>
-      <c r="AN22" t="n">
-        <v>500.0058333333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>499.9410714285715</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>499.8075</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>499.8836111111112</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>500.1534999999999</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>62.21146721260463</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>59.05175195094854</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>57.61829528127778</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>59.02435390691848</v>
-      </c>
       <c r="AW22" t="n">
-        <v>59.81951840489536</v>
+        <v>500.0054999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>59.9838455776878</v>
+        <v>499.9409999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>60.47784914420322</v>
+        <v>499.8089999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>60.27347955022343</v>
+        <v>499.8845</v>
       </c>
       <c r="BA22" t="n">
-        <v>59.90204359509566</v>
+        <v>500.1539999999999</v>
       </c>
       <c r="BB22" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>59.05150000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>57.6185</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>59.024</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>59.81950000000001</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>59.9845</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>60.4775</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>60.2735</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>59.9025</v>
+      </c>
+      <c r="BK22" t="n">
         <v>351.5</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>351.5</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>351.05</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>349.9</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>349.9</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>349.9</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>349.8</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>349.8</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>349.8</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>643.3</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>643.85</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>643.85</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>643.85</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>643.85</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>644</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>644.1</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>644.1</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>644.1</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6485998478645537</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7500567311229076</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7171339700089701</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.790336107554662</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7919135262941933</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8267667169562726</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.8272365234691075</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8355716208846665</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8594171459683976</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>481.0945</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>45.748</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.468081454788778</v>
       </c>
       <c r="C23" t="n">
+        <v>2.256147991853761</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.521771820505364</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.256147991853761</v>
       </c>
       <c r="E23" t="n">
         <v>1.468081454788778</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03773174009406822</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.720618004029213</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2770003800111397</v>
+      </c>
       <c r="I23" t="n">
-        <v>10.97511317862366</v>
+        <v>0.2800653119316428</v>
       </c>
       <c r="J23" t="n">
-        <v>10.86105961346677</v>
+        <v>0.256294957545321</v>
       </c>
       <c r="K23" t="n">
-        <v>10.0151300359183</v>
+        <v>0.2247361025502438</v>
       </c>
       <c r="L23" t="n">
-        <v>8.896427627209286</v>
+        <v>0.2029363395125103</v>
       </c>
       <c r="M23" t="n">
-        <v>8.634268037269221</v>
+        <v>0.2008010274664424</v>
       </c>
       <c r="N23" t="n">
-        <v>7.249314902851314</v>
+        <v>0.2009948938864395</v>
       </c>
       <c r="O23" t="n">
-        <v>7.36603111570902</v>
+        <v>0.2527720004480843</v>
       </c>
       <c r="P23" t="n">
-        <v>8.410822571032602</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7.482107097275946</v>
-      </c>
+        <v>0.2795348580089884</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>9.083024910813672</v>
+        <v>10.97574555674082</v>
       </c>
       <c r="S23" t="n">
-        <v>7.909181638659808</v>
+        <v>10.86048185177028</v>
       </c>
       <c r="T23" t="n">
-        <v>7.490683583827904</v>
+        <v>10.01453179660752</v>
       </c>
       <c r="U23" t="n">
-        <v>7.435381484716078</v>
+        <v>8.896052273488031</v>
       </c>
       <c r="V23" t="n">
-        <v>6.440084172027809</v>
+        <v>8.634476792121463</v>
       </c>
       <c r="W23" t="n">
-        <v>7.624534287024485</v>
+        <v>7.248812080537567</v>
       </c>
       <c r="X23" t="n">
-        <v>6.632202269361718</v>
+        <v>7.366879561502564</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.884314229320247</v>
+        <v>8.409736759757765</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.707901780571687</v>
+        <v>7.481305543257738</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>9.081693211012325</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>7.909606484322846</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>7.490616498414252</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>7.435669562460754</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>6.439192720732691</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>7.623350468686388</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>6.632961075687008</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>7.883916656212522</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.708159994807065</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.336879993662537</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.323303002646296</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.746887622353418</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.337666061313224</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.32410814813135</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.746699971223932</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1.604654742337198</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.510847957177568</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.515513892275463</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.712946061767946</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.6773424893297</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.53926768302333</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>10.33558001351682</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.702712313057168</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.02176585540421</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>7.642767883212978</v>
-      </c>
       <c r="AW23" t="n">
-        <v>7.911738246232431</v>
+        <v>1.510184634930099</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.58958999427965</v>
+        <v>1.515217198257311</v>
       </c>
       <c r="AY23" t="n">
-        <v>6.508161405901177</v>
+        <v>1.713257592700924</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.240354553967904</v>
+        <v>1.678340267237717</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.049944160791282</v>
+        <v>1.538931276465659</v>
       </c>
       <c r="BB23" t="n">
+        <v>10.33576009987196</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>8.703467714834007</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8.021546822219056</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7.642861409597574</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>7.911170300677126</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>7.588670554812199</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>6.508758370558535</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>6.241737506917699</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>6.049761087061728</v>
+      </c>
+      <c r="BK23" t="n">
         <v>26.43661734870982</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>26.43661734870982</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>25.50227028077469</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>23.73072625144567</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>23.73072625144567</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>23.73072625144567</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>23.5385462145549</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>23.5385462145549</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>23.5385462145549</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>28.97567037506139</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>27.66581588207824</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>27.66581588207824</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>27.66581588207824</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>27.66581588207824</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>27.35920897594581</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>27.1620865797976</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>27.1620865797976</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>27.1620865797976</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.3072156135310363</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2329707266370573</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2698200368607753</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1429747457390773</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1495563767046274</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1384907659745555</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.129149182660616</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.1154878368593102</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1169899030073311</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>7.883916656212522</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>5.708159994807065</v>
       </c>
     </row>
   </sheetData>
